--- a/data_src/xlsx表/站子等级表.xlsx
+++ b/data_src/xlsx表/站子等级表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,6 +527,121 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>百粉草站</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>五百粉小站</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>500</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>千粉站</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>五千粉大站</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>万粉知名站</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_src/xlsx表/站子等级表.xlsx
+++ b/data_src/xlsx表/站子等级表.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,33 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +59,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,234 +453,320 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>thresholdexp</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>hotcountgoal</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>rewardfp</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>postcapbonus</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>rewarditemid</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>rewarditemcount</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>idolkara</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>videocallid</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>等级</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>所需站子经验阈值</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>等级奖励道具编号</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>奖励数量</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0普通生咖/1艺人出席生咖</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>影通事件 id（预留）</t>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>粉丝阈值</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>热门次数</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>奖励积分</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>发帖上限</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>生咖</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>影通</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>百粉草站</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>100</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>五百粉小站</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>500</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>千粉站</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>五千粉大站</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>万粉知名站</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>千粉大站</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
